--- a/output/stock_quant_scores/META_income_df.xlsx
+++ b/output/stock_quant_scores/META_income_df.xlsx
@@ -1267,7 +1267,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>47307000000</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1278,13 +1280,17 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>13.99</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>39370000000</v>
+      </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1308,9 +1314,13 @@
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>95280000000</v>
+      </c>
       <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>117929000000</v>
+      </c>
       <c r="AW6" t="inlineStr"/>
     </row>
   </sheetData>
